--- a/output/stock_quant_scores/PLTR_info.xlsx
+++ b/output/stock_quant_scores/PLTR_info.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FO2"/>
+  <dimension ref="A1:FS2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1046,235 +1046,255 @@
       </c>
       <c r="DU1" s="1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketPrice</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChange</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="EE1" s="1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="EF1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="EG1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="EH1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="EI1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EJ1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EK1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EL1" s="1" t="inlineStr">
         <is>
           <t>earningsTimestamp</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="EM1" s="1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="EN1" s="1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="EO1" s="1" t="inlineStr">
         <is>
           <t>earningsCallTimestampStart</t>
         </is>
       </c>
-      <c r="EG1" s="1" t="inlineStr">
+      <c r="EP1" s="1" t="inlineStr">
         <is>
           <t>earningsCallTimestampEnd</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="EQ1" s="1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="EI1" s="1" t="inlineStr">
+      <c r="ER1" s="1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="EJ1" s="1" t="inlineStr">
+      <c r="ES1" s="1" t="inlineStr">
         <is>
           <t>epsForward</t>
         </is>
       </c>
-      <c r="EK1" s="1" t="inlineStr">
+      <c r="ET1" s="1" t="inlineStr">
         <is>
           <t>epsCurrentYear</t>
         </is>
       </c>
-      <c r="EL1" s="1" t="inlineStr">
+      <c r="EU1" s="1" t="inlineStr">
         <is>
           <t>priceEpsCurrentYear</t>
         </is>
       </c>
-      <c r="EM1" s="1" t="inlineStr">
+      <c r="EV1" s="1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="EN1" s="1" t="inlineStr">
+      <c r="EW1" s="1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EO1" s="1" t="inlineStr">
+      <c r="EX1" s="1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="EP1" s="1" t="inlineStr">
+      <c r="EY1" s="1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EQ1" s="1" t="inlineStr">
+      <c r="EZ1" s="1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="ER1" s="1" t="inlineStr">
+      <c r="FA1" s="1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="ES1" s="1" t="inlineStr">
+      <c r="FB1" s="1" t="inlineStr">
         <is>
           <t>ipoExpectedDate</t>
         </is>
       </c>
-      <c r="ET1" s="1" t="inlineStr">
+      <c r="FC1" s="1" t="inlineStr">
         <is>
           <t>averageAnalystRating</t>
         </is>
       </c>
-      <c r="EU1" s="1" t="inlineStr">
+      <c r="FD1" s="1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="FE1" s="1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="FF1" s="1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="FG1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketTime</t>
+        </is>
+      </c>
+      <c r="FH1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="FI1" s="1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="FJ1" s="1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="FK1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="FL1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="FM1" s="1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="FN1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="FO1" s="1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="FP1" s="1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="FQ1" s="1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="EV1" s="1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EW1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EX1" s="1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EY1" s="1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EZ1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="FA1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="FB1" s="1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="FC1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="FD1" s="1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="FE1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="FF1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="FG1" s="1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="FH1" s="1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="FI1" s="1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="FJ1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="FK1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="FL1" s="1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="FM1" s="1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="FN1" s="1" t="inlineStr">
+      <c r="FR1" s="1" t="inlineStr">
         <is>
           <t>displayName</t>
         </is>
       </c>
-      <c r="FO1" s="1" t="inlineStr">
+      <c r="FS1" s="1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -1400,28 +1420,28 @@
         <v>2</v>
       </c>
       <c r="AC2" t="n">
-        <v>182.55</v>
+        <v>179.12</v>
       </c>
       <c r="AD2" t="n">
-        <v>183.91</v>
+        <v>178.935</v>
       </c>
       <c r="AE2" t="n">
-        <v>177.14</v>
+        <v>174.92</v>
       </c>
       <c r="AF2" t="n">
-        <v>184.85</v>
+        <v>180.12</v>
       </c>
       <c r="AG2" t="n">
-        <v>182.55</v>
+        <v>179.12</v>
       </c>
       <c r="AH2" t="n">
-        <v>183.91</v>
+        <v>178.935</v>
       </c>
       <c r="AI2" t="n">
-        <v>177.12</v>
+        <v>174.91</v>
       </c>
       <c r="AJ2" t="n">
-        <v>184.85</v>
+        <v>180.12</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
@@ -1430,40 +1450,40 @@
         <v>2.592</v>
       </c>
       <c r="AM2" t="n">
-        <v>614.7931</v>
+        <v>591.9</v>
       </c>
       <c r="AN2" t="n">
-        <v>379.34042</v>
+        <v>377.80853</v>
       </c>
       <c r="AO2" t="n">
-        <v>35064016</v>
+        <v>43153101</v>
       </c>
       <c r="AP2" t="n">
-        <v>35064136</v>
+        <v>43153101</v>
       </c>
       <c r="AQ2" t="n">
-        <v>69779334</v>
+        <v>67058128</v>
       </c>
       <c r="AR2" t="n">
-        <v>59601840</v>
+        <v>59932140</v>
       </c>
       <c r="AS2" t="n">
-        <v>59601840</v>
+        <v>59932140</v>
       </c>
       <c r="AT2" t="n">
-        <v>177.94</v>
+        <v>163.15</v>
       </c>
       <c r="AU2" t="n">
-        <v>185</v>
+        <v>186.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW2" t="n">
         <v>1</v>
       </c>
       <c r="AX2" t="n">
-        <v>422964920320</v>
+        <v>421256888320</v>
       </c>
       <c r="AY2" t="n">
         <v>36.05</v>
@@ -1478,13 +1498,13 @@
         <v>5.92</v>
       </c>
       <c r="BC2" t="n">
-        <v>122.933945</v>
+        <v>122.43751</v>
       </c>
       <c r="BD2" t="n">
-        <v>164.4382</v>
+        <v>166.0936</v>
       </c>
       <c r="BE2" t="n">
-        <v>117.26035</v>
+        <v>118.8513</v>
       </c>
       <c r="BF2" t="n">
         <v>0</v>
@@ -1501,7 +1521,7 @@
         <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>427405148160</v>
+        <v>415590907904</v>
       </c>
       <c r="BK2" t="n">
         <v>0.22185</v>
@@ -1513,31 +1533,31 @@
         <v>2274261581</v>
       </c>
       <c r="BN2" t="n">
-        <v>49337540</v>
+        <v>54581338</v>
       </c>
       <c r="BO2" t="n">
-        <v>54757082</v>
+        <v>53973790</v>
       </c>
       <c r="BP2" t="n">
-        <v>1753920000</v>
+        <v>1755216000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1756425600</v>
+        <v>1757894400</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.0208</v>
+        <v>0.023</v>
       </c>
       <c r="BS2" t="n">
         <v>0.03615</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.57375</v>
+        <v>0.574</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.0227</v>
+        <v>0.0251</v>
       </c>
       <c r="BW2" t="n">
         <v>2372342421</v>
@@ -1546,7 +1566,7 @@
         <v>2.5</v>
       </c>
       <c r="BY2" t="n">
-        <v>71.315994</v>
+        <v>71.02800000000001</v>
       </c>
       <c r="BZ2" t="n">
         <v>1735603200</v>
@@ -1564,22 +1584,22 @@
         <v>763292032</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="CF2" t="n">
         <v>0.47</v>
       </c>
       <c r="CG2" t="n">
-        <v>124.224</v>
+        <v>120.791</v>
       </c>
       <c r="CH2" t="n">
-        <v>714.972</v>
+        <v>695.2089999999999</v>
       </c>
       <c r="CI2" t="n">
-        <v>3.9178343</v>
+        <v>3.773387</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.16333759</v>
+        <v>0.1529237</v>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
@@ -1587,7 +1607,7 @@
         </is>
       </c>
       <c r="CL2" t="n">
-        <v>178.29</v>
+        <v>177.57</v>
       </c>
       <c r="CM2" t="n">
         <v>215</v>
@@ -1709,174 +1729,186 @@
       </c>
       <c r="DU2" t="inlineStr">
         <is>
+          <t>Palantir Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="DW2" t="n">
+        <v>-0.865335</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>177.57</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>-0.078850396</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>177.43</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>-0.14001465</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>-1.54999</v>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>174.91 - 180.12</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
           <t>NasdaqGS</t>
         </is>
       </c>
-      <c r="DV2" t="n">
-        <v>69779334</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>142.23999</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>3.9456308</v>
-      </c>
-      <c r="DY2" t="inlineStr">
+      <c r="EE2" t="n">
+        <v>67058128</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>141.52</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>3.925659</v>
+      </c>
+      <c r="EH2" t="inlineStr">
         <is>
           <t>36.05 - 190.0</t>
         </is>
       </c>
-      <c r="DZ2" t="n">
-        <v>-11.710007</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>-0.061631612</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>391.78342</v>
-      </c>
-      <c r="EC2" t="n">
+      <c r="EI2" t="n">
+        <v>-12.429993</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>-0.065421015</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>377.33868</v>
+      </c>
+      <c r="EL2" t="n">
         <v>1754337600</v>
       </c>
-      <c r="ED2" t="n">
+      <c r="EM2" t="n">
         <v>1762200000</v>
       </c>
-      <c r="EE2" t="n">
+      <c r="EN2" t="n">
         <v>1762200000</v>
       </c>
-      <c r="EF2" t="n">
+      <c r="EO2" t="n">
         <v>1754341200</v>
       </c>
-      <c r="EG2" t="n">
+      <c r="EP2" t="n">
         <v>1754341200</v>
       </c>
-      <c r="EH2" t="b">
+      <c r="EQ2" t="b">
         <v>1</v>
       </c>
-      <c r="EI2" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="EJ2" t="n">
+      <c r="ER2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="ES2" t="n">
         <v>0.47</v>
       </c>
-      <c r="EK2" t="n">
+      <c r="ET2" t="n">
         <v>0.6424800000000001</v>
       </c>
-      <c r="EL2" t="n">
-        <v>277.50278</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>13.851791</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>0.08423706</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>61.02964</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>0.5204626999999999</v>
-      </c>
-      <c r="EQ2" t="n">
+      <c r="EU2" t="n">
+        <v>276.38214</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>11.47641</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>0.06909604</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>58.718704</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>0.49405184</v>
+      </c>
+      <c r="EZ2" t="n">
         <v>15</v>
       </c>
-      <c r="ER2" t="n">
+      <c r="FA2" t="n">
         <v>0</v>
       </c>
-      <c r="ES2" t="inlineStr">
+      <c r="FB2" t="inlineStr">
         <is>
           <t>2024-11-26</t>
         </is>
       </c>
-      <c r="ET2" t="inlineStr">
+      <c r="FC2" t="inlineStr">
         <is>
           <t>3.0 - Hold</t>
         </is>
       </c>
-      <c r="EU2" t="b">
+      <c r="FD2" t="b">
+        <v>1</v>
+      </c>
+      <c r="FE2" t="n">
+        <v>1601472600000</v>
+      </c>
+      <c r="FF2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="FG2" t="n">
+        <v>1758931194</v>
+      </c>
+      <c r="FH2" t="n">
+        <v>1758916800</v>
+      </c>
+      <c r="FI2" t="inlineStr">
+        <is>
+          <t>NMS</t>
+        </is>
+      </c>
+      <c r="FJ2" t="inlineStr">
+        <is>
+          <t>finmb_43580005</t>
+        </is>
+      </c>
+      <c r="FK2" t="inlineStr">
+        <is>
+          <t>America/New_York</t>
+        </is>
+      </c>
+      <c r="FL2" t="inlineStr">
+        <is>
+          <t>EDT</t>
+        </is>
+      </c>
+      <c r="FM2" t="n">
+        <v>-14400000</v>
+      </c>
+      <c r="FN2" t="inlineStr">
+        <is>
+          <t>us_market</t>
+        </is>
+      </c>
+      <c r="FO2" t="b">
         <v>0</v>
       </c>
-      <c r="EV2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EW2" t="n">
-        <v>1758740028</v>
-      </c>
-      <c r="EX2" t="inlineStr">
-        <is>
-          <t>NMS</t>
-        </is>
-      </c>
-      <c r="EY2" t="inlineStr">
-        <is>
-          <t>finmb_43580005</t>
-        </is>
-      </c>
-      <c r="EZ2" t="inlineStr">
-        <is>
-          <t>America/New_York</t>
-        </is>
-      </c>
-      <c r="FA2" t="inlineStr">
-        <is>
-          <t>EDT</t>
-        </is>
-      </c>
-      <c r="FB2" t="n">
-        <v>-14400000</v>
-      </c>
-      <c r="FC2" t="inlineStr">
-        <is>
-          <t>us_market</t>
-        </is>
-      </c>
-      <c r="FD2" t="b">
+      <c r="FP2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="FQ2" t="b">
         <v>0</v>
       </c>
-      <c r="FE2" t="n">
-        <v>-2.3336124</v>
-      </c>
-      <c r="FF2" t="n">
-        <v>178.29</v>
-      </c>
-      <c r="FG2" t="inlineStr">
-        <is>
-          <t>Palantir Technologies Inc.</t>
-        </is>
-      </c>
-      <c r="FH2" t="inlineStr">
-        <is>
-          <t>Palantir Technologies Inc.</t>
-        </is>
-      </c>
-      <c r="FI2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="FJ2" t="n">
-        <v>-4.26001</v>
-      </c>
-      <c r="FK2" t="inlineStr">
-        <is>
-          <t>177.12 - 184.85</t>
-        </is>
-      </c>
-      <c r="FL2" t="b">
-        <v>1</v>
-      </c>
-      <c r="FM2" t="n">
-        <v>1601472600000</v>
-      </c>
-      <c r="FN2" t="inlineStr">
+      <c r="FR2" t="inlineStr">
         <is>
           <t>Palantir</t>
         </is>
       </c>
-      <c r="FO2" t="n">
-        <v>3.535</v>
+      <c r="FS2" t="n">
+        <v>3.4386</v>
       </c>
     </row>
   </sheetData>
